--- a/stories/arbres/ATOM-JEU.REG.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Antonin joue aux cubes avec Alix. Alix finit sa tour. L'autre peut gagner. Antonin sent une boule. Il dit : je suis déçu. C'est permis. Maman dit : on peut rejouer plus tard. Antonin dit bravo. Il souffle. Ils rangeront. Plus tard, ils rejoueront. L'autre peut gagner. Déçu permis. Rejouer plus tard.</t>
+          <t>Antonin joue aux cubes avec Alix. Alix finit sa tour. L'autre peut gagner. Antonin sent une boule. Je suis déçu. C'est permis. On peut rejouer plus tard. Antonin dit bravo. Il souffle. Ils rangeront. Plus tard, ils rejoueront. L'autre peut gagner. Déçu permis. Rejouer plus tard.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Antonin joue aux cubes avec Alix. Alix finit sa tour. L'autre peut gagner. Antonin sent une boule.
+narrateur|Je suis déçu. C'est permis.
+maman|On peut rejouer plus tard.
+narrateur|Antonin dit bravo. Il souffle. Ils rangeront. Plus tard, ils rejoueront. L'autre peut gagner. Déçu permis. Rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Alix gagne. Que peut faire Antonin ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Antonin a dit bravo. Il était déçu. C'est permis. Ils rejoueront plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range un cube. Antonin donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 narrateur|Antonin dit bravo. Il souffle. Ils rangeront. Plus tard, ils rejoueront. L'autre peut gagner. Déçu permis. Rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|Alix gagne. Que peut faire Antonin ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Antonin a dit bravo. Il était déçu. C'est permis. Ils rejoueront plus tard.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Maman range un cube. Antonin donne la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.REG.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Antonin accepte de perdre</t>
+          <t>La tour de Nina, le doudou de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah voit Nina finir sa tour. Elle nomme sa déception, dit bravo, et elles rejoueront plus tard.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Antonin joue aux cubes avec Alix. Alix finit sa tour. L'autre peut gagner. Antonin sent une boule. Je suis déçu. C'est permis. On peut rejouer plus tard. Antonin dit bravo. Il souffle. Ils rangeront. Plus tard, ils rejoueront. L'autre peut gagner. Déçu permis. Rejouer plus tard.</t>
+          <t>Le doudou de Sarah pend au bras du canapé. Il attend, tout mou, près du coussin. Un cube bleu est sous la table. La soupe sent bon, depuis la cuisine. Le tapis est épais sous les genoux. Un rayon se pose sur le coussin. Le doudou a une oreille un peu plate. Un cube vert brille, tout près. Tu as vu ton doudou, Sarah ? Oui. Il attend. En ce moment, Nina pose un cube rouge. Sarah pose un cube jaune, tout près. Le mien est jaune. Oui. Chacune sa tour de cubes. Nina ajoute encore un cube. Sa tour devient plus haute. Nina pose le dernier cube. Sa tour est finie. Nina a fini. L'autre peut gagner. Sarah sent une boule dans le ventre. Je suis déçue. Être déçue, c'est permis. Sarah souffle. Le doudou pend encore. Bravo, Nina. Merci, Sarah. Tu as dit bravo. On peut rejouer plus tard. Plus tard ? Oui. D'abord on range un peu. Sarah range un cube bleu. Nina range un cube rouge. Vous rangez les cubes ensemble ? Oui, maman. Bravo. Plus tard, on rejoue. Sarah prend le doudou contre sa joue. Il est doux. Il sent le lit. L'autre peut gagner. Oui. Et c'est permis d'être déçue. On dit bravo. On rejoue plus tard. On rejoue plus tard. Tu as dit bravo. Bravo, Sarah. Tu as fait du bon travail. La soupe sent encore, tout près. J'ai encore la boule. C'est permis. On va manger un peu. Sarah range encore un cube jaune. Nina pose sa tour, cube par cube, dans la caisse. Tu as dit bravo. L'autre peut gagner. On rejoue plus tard. Oui. Après la soupe.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Antonin joue aux cubes avec Alix. Alix finit sa tour. L'autre peut gagner. Antonin sent une boule.
-narrateur|Je suis déçu. C'est permis.
+          <t>narrateur|Le doudou de Sarah pend au bras du canapé.
+narrateur|Il attend, tout mou, près du coussin.
+narrateur|Un cube bleu est sous la table.
+narrateur|La soupe sent bon, depuis la cuisine.
+narrateur|Le tapis est épais sous les genoux.
+narrateur|Un rayon se pose sur le coussin.
+narrateur|Le doudou a une oreille un peu plate.
+narrateur|Un cube vert brille, tout près.
+maman|Tu as vu ton doudou, Sarah ?
+enfant-f|Oui. Il attend.
+narrateur|En ce moment, Nina pose un cube rouge.
+narrateur|Sarah pose un cube jaune, tout près.
+enfant-f|Le mien est jaune.
+maman|Oui. Chacune sa tour de cubes.
+narrateur|Nina ajoute encore un cube.
+narrateur|Sa tour devient plus haute.
+narrateur|Nina pose le dernier cube.
+narrateur|Sa tour est finie.
+maman|Nina a fini. L'autre peut gagner.
+narrateur|Sarah sent une boule dans le ventre.
+enfant-f|Je suis déçue.
+maman|Être déçue, c'est permis.
+narrateur|Sarah souffle. Le doudou pend encore.
+enfant-f|Bravo, Nina.
+maman|Merci, Sarah. Tu as dit bravo.
 maman|On peut rejouer plus tard.
-narrateur|Antonin dit bravo. Il souffle. Ils rangeront. Plus tard, ils rejoueront. L'autre peut gagner. Déçu permis. Rejouer plus tard.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-f|Plus tard ?
+maman|Oui. D'abord on range un peu.
+narrateur|Sarah range un cube bleu.
+narrateur|Nina range un cube rouge.
+maman|Vous rangez les cubes ensemble ?
+enfant-f|Oui, maman.
+maman|Bravo. Plus tard, on rejoue.
+narrateur|Sarah prend le doudou contre sa joue.
+narrateur|Il est doux. Il sent le lit.
+enfant-f|L'autre peut gagner.
+maman|Oui. Et c'est permis d'être déçue.
+maman|On dit bravo. On rejoue plus tard.
+enfant-f|On rejoue plus tard.
+maman|Tu as dit bravo. Bravo, Sarah.
+maman|Tu as fait du bon travail.
+narrateur|La soupe sent encore, tout près.
+enfant-f|J'ai encore la boule.
+maman|C'est permis. On va manger un peu.
+narrateur|Sarah range encore un cube jaune.
+narrateur|Nina pose sa tour, cube par cube, dans la caisse.
+maman|Tu as dit bravo. L'autre peut gagner.
+enfant-f|On rejoue plus tard.
+maman|Oui. Après la soupe.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,7 +1399,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Alix gagne. Que peut faire Antonin ?</t>
+          <t>Nina gagne. Que peut faire Sarah ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1499,10 +1555,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Alix gagne. Que peut faire Antonin ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nina gagne.
+narrateur|Que peut faire Sarah ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1527,7 +1583,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Antonin a dit bravo. Il était déçu. C'est permis. Ils rejoueront plus tard.</t>
+          <t>Sarah a dit bravo. Elle était déçue. C'est permis. Elles rejoueront plus tard. Tu as dit bravo à Nina ? Oui, maman. Bravo. L'autre peut gagner. Le doudou reste contre la joue de Sarah.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1671,10 +1727,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Antonin a dit bravo. Il était déçu. C'est permis. Ils rejoueront plus tard.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah a dit bravo.
+narrateur|Elle était déçue. C'est permis.
+narrateur|Elles rejoueront plus tard.
+maman|Tu as dit bravo à Nina ?
+enfant-f|Oui, maman.
+maman|Bravo. L'autre peut gagner.
+narrateur|Le doudou reste contre la joue de Sarah.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1699,7 +1760,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range un cube. Antonin donne la main.</t>
+          <t>Maman range un cube. Sarah donne la main. On va vers la soupe ? Oui. Elle sent bon. Nina vient aussi, tout près. Plus tard, on rejoue. Oui. Plus tard. Le doudou reste sur le canapé. La caisse de cubes est fermée.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1839,10 +1900,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range un cube. Antonin donne la main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Maman range un cube.
+narrateur|Sarah donne la main.
+maman|On va vers la soupe ?
+enfant-f|Oui. Elle sent bon.
+narrateur|Nina vient aussi, tout près.
+enfant-f|Plus tard, on rejoue.
+maman|Oui. Plus tard.
+narrateur|Le doudou reste sur le canapé.
+narrateur|La caisse de cubes est fermée.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1867,7 +1935,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La soupe fume dans les bols. J'étais déçue. C'était permis. Oui. Tu as dit bravo. On rejoue plus tard. Bravo, Sarah. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2007,10 +2075,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La soupe fume dans les bols.
+enfant-f|J'étais déçue. C'était permis.
+maman|Oui. Tu as dit bravo.
+maman|On rejoue plus tard.
+maman|Bravo, Sarah.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2029,7 +2101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2139,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le doudou de Sarah pend au bras du canapé. Il attend, tout mou, près du coussin. Un cube bleu est sous la table. La soupe sent bon, depuis la cuisine. Le tapis est épais sous les genoux. Un rayon se pose sur le coussin. Le doudou a une oreille un peu plate. Un cube vert brille, tout près. Tu as vu ton doudou, Sarah ? Oui. Il attend. En ce moment, Nina pose un cube rouge. Sarah pose un cube jaune, tout près. Le mien est jaune. Oui. Chacune sa tour de cubes. Nina ajoute encore un cube. Sa tour devient plus haute. Nina pose le dernier cube. Sa tour est finie. Nina a fini. L'autre peut gagner. Sarah sent une boule dans le ventre. Je suis déçue. Être déçue, c'est permis. Sarah souffle. Le doudou pend encore. Bravo, Nina. Merci, Sarah. Tu as dit bravo. On peut rejouer plus tard. Plus tard ? Oui. D'abord on range un peu. Sarah range un cube bleu. Nina range un cube rouge. Vous rangez les cubes ensemble ? Oui, maman. Bravo. Plus tard, on rejoue. Sarah prend le doudou contre sa joue. Il est doux. Il sent le lit. L'autre peut gagner. Oui. Et c'est permis d'être déçue. On dit bravo. On rejoue plus tard. On rejoue plus tard. Tu as dit bravo. Bravo, Sarah. Tu as fait du bon travail. La soupe sent encore, tout près. J'ai encore la boule. C'est permis. On va manger un peu. Sarah range encore un cube jaune. Nina pose sa tour, cube par cube, dans la caisse. Tu as dit bravo. L'autre peut gagner. On rejoue plus tard. Oui. Après la soupe.</t>
+          <t>Le doudou de Sarah pend au bras du canapé. Il attend, tout mou, près du coussin. Un cube bleu est sous la table. La soupe sent bon, depuis la cuisine. Le tapis est épais sous les genoux. Un rayon se pose sur le coussin. Le doudou a une oreille un peu plate. Un cube vert brille, tout près. Tu as vu ton doudou, Sarah ? Oui. Il attend. En ce moment, Nina pose un cube rouge. Sarah pose un cube jaune, tout près. Le mien est jaune. Oui. Chacune sa tour de cubes. Nina ajoute encore un cube. Sa tour devient plus haute. Nina pose le dernier cube. Sa tour est finie. Nina a fini. L'autre peut gagner. Sarah sent une boule dans le ventre. Je suis déçue. Être déçue, c'est permis. Sarah souffle. Le doudou pend encore. Bravo, Nina. Merci, Sarah. Tu as dit bravo. On peut rejouer plus tard. Plus tard ? Oui. D'abord on range un peu. Sarah range un cube bleu. Nina range un cube rouge. Vous rangez les cubes ensemble ? Oui, maman. Bravo. Plus tard, on rejoue. Sarah prend le doudou contre sa joue. Il est doux. Il sent le lit. L'autre peut gagner. Oui. Et c'est permis d'être déçue. On dit bravo. On rejoue plus tard. On rejoue plus tard. Tu as dit bravo. Bravo, Sarah. La soupe sent encore, tout près. J'ai encore la boule. C'est permis. On va manger un peu. Sarah range encore un cube jaune. Nina pose sa tour, cube par cube, dans la caisse. Tu as dit bravo. L'autre peut gagner. On rejoue plus tard. Oui. Après la soupe.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Antonin joue aux cubes avec Alix. Alix finit sa tour. &lt;emphasis level="moderate"&gt;l'autre&lt;/emphasis&gt; peut gagner. Antonin sent une boule. Il dit : je suis déçu. C'est permis. Maman dit : on peut rejouer plus tard. Antonin dit bravo. Il souffle. Ils rangeront. Plus tard, ils rejoueront. L'autre peut gagner. Déçu permis. Rejouer plus tard.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le doudou de Sarah pend au bras du canapé. Il attend, tout mou, près du coussin. Un cube bleu est sous la table. La soupe sent bon, depuis la cuisine. Le tapis est épais sous les genoux. Un rayon se pose sur le coussin. Le doudou a une oreille un peu plate. Un cube vert brille, tout près. Tu as vu ton doudou, Sarah ? Oui. Il attend. En ce moment, Nina pose un cube rouge. Sarah pose un cube jaune, tout près. Le mien est jaune. Oui. Chacune sa tour de cubes. Nina ajoute encore un cube. Sa tour devient plus haute. Nina pose le dernier cube. Sa tour est finie. Nina a fini. L'autre peut gagner. Sarah sent une boule dans le ventre. Je suis déçue. Être déçue, c'est permis. Sarah souffle. Le doudou pend encore. Bravo, Nina. Merci, Sarah. Tu as dit bravo. On peut rejouer plus tard. Plus tard ? Oui. D'abord on range un peu. Sarah range un cube bleu. Nina range un cube rouge. Vous rangez les cubes ensemble ? Oui, maman. Bravo. Plus tard, on rejoue. Sarah prend le doudou contre sa joue. Il est doux. Il sent le lit. L'autre peut gagner. Oui. Et c'est permis d'être déçue. On dit bravo. On rejoue plus tard. On rejoue plus tard. Tu as dit bravo. Bravo, Sarah. La soupe sent encore, tout près. J'ai encore la boule. C'est permis. On va manger un peu. Sarah range encore un cube jaune. Nina pose sa tour, cube par cube, dans la caisse. Tu as dit bravo. L'autre peut gagner. On rejoue plus tard. Oui. Après la soupe.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1364,7 +1364,6 @@
 maman|On dit bravo. On rejoue plus tard.
 enfant-f|On rejoue plus tard.
 maman|Tu as dit bravo. Bravo, Sarah.
-maman|Tu as fait du bon travail.
 narrateur|La soupe sent encore, tout près.
 enfant-f|J'ai encore la boule.
 maman|C'est permis. On va manger un peu.
@@ -1404,7 +1403,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Alix gagne. Que peut faire Antonin ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina gagne. Que peut faire Sarah ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1588,7 +1587,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Antonin a dit bravo. Il était &lt;emphasis level="moderate"&gt;déçu&lt;/emphasis&gt;. C'est permis. Ils rejoueront plus tard.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a dit bravo. Elle était déçue. C'est permis. Elles rejoueront plus tard. Tu as dit bravo à Nina ? Oui, maman. Bravo. L'autre peut gagner. Le doudou reste contre la joue de Sarah.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1765,7 +1764,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range un cube. Antonin donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman range un cube. Sarah donne la main. On va vers la soupe ? Oui. Elle sent bon. Nina vient aussi, tout près. Plus tard, on rejoue. Oui. Plus tard. Le doudou reste sur le canapé. La caisse de cubes est fermée.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1935,12 +1934,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La soupe fume dans les bols. J'étais déçue. C'était permis. Oui. Tu as dit bravo. On rejoue plus tard. Bravo, Sarah. L'histoire est finie.</t>
+          <t>La soupe fume dans les bols. J'étais déçue. C'était permis. Oui. Tu as dit bravo. On rejoue plus tard. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La soupe fume dans les bols. J'étais déçue. C'était permis. Oui. Tu as dit bravo. On rejoue plus tard. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2079,8 +2078,7 @@
 enfant-f|J'étais déçue. C'était permis.
 maman|Oui. Tu as dit bravo.
 maman|On rejoue plus tard.
-maman|Bravo, Sarah.
-narrateur|L'histoire est finie.</t>
+maman|Bravo, Sarah.</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2146,6 +2144,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>salon, tapis près du canapé</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Antonin, Alix, maman</t>
+          <t>Sarah, Nina, maman</t>
         </is>
       </c>
     </row>
